--- a/grupos/3ARHV - Estadisticos 20241.xlsx
+++ b/grupos/3ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -164,27 +164,27 @@
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,45 +197,54 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CALVA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -248,76 +257,91 @@
     <t>XICALHUA</t>
   </si>
   <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
     <t>LORENA</t>
   </si>
   <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
     <t>DORIAN</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
@@ -875,28 +899,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -926,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -941,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="AF4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>-1</v>
@@ -976,28 +1000,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1024,25 +1048,25 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>9</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG5">
         <v>-1</v>
@@ -1077,28 +1101,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1128,22 +1152,22 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
         <v>8</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1178,28 +1202,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1229,19 +1253,19 @@
         <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF7">
         <v>8</v>
@@ -1279,28 +1303,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1327,13 +1351,13 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1345,7 +1369,7 @@
         <v>6</v>
       </c>
       <c r="AF8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>-1</v>
@@ -1380,28 +1404,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1428,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1443,10 +1467,10 @@
         <v>8</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>-1</v>
@@ -1481,28 +1505,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1529,25 +1553,25 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>-1</v>
@@ -1582,28 +1606,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1630,7 +1654,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>6</v>
@@ -1642,10 +1666,10 @@
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF11">
         <v>8</v>
@@ -1683,28 +1707,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1731,7 +1755,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>6</v>
@@ -1749,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG12">
         <v>-1</v>
@@ -1784,28 +1808,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1835,7 +1859,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1844,13 +1868,13 @@
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE13">
         <v>10</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>-1</v>
@@ -1885,28 +1909,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1933,7 +1957,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1942,16 +1966,16 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE14">
         <v>8</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>-1</v>
@@ -1986,28 +2010,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2037,22 +2061,22 @@
         <v>10</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>10</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -2087,28 +2111,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2135,13 +2159,13 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>9</v>
@@ -2150,10 +2174,10 @@
         <v>7</v>
       </c>
       <c r="AE16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG16">
         <v>-1</v>
@@ -2188,28 +2212,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2239,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2289,28 +2313,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2337,25 +2361,25 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>8</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2390,28 +2414,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2438,10 +2462,10 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2453,10 +2477,10 @@
         <v>7</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>-1</v>
@@ -2491,28 +2515,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2542,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>9</v>
@@ -2551,13 +2575,13 @@
         <v>10</v>
       </c>
       <c r="AD20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>-1</v>
@@ -2592,28 +2616,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2643,19 +2667,19 @@
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF21">
         <v>6</v>
@@ -2693,28 +2717,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2741,25 +2765,25 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>6</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2794,28 +2818,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2845,22 +2869,22 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB23">
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG23">
         <v>-1</v>
@@ -2895,28 +2919,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2943,7 +2967,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2958,10 +2982,10 @@
         <v>7</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG24">
         <v>-1</v>
@@ -3136,16 +3160,16 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -3160,16 +3184,16 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W4">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X4">
         <v>100</v>
@@ -3213,16 +3237,16 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>94.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3237,16 +3261,16 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>94.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -3290,16 +3314,16 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O6">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3314,16 +3338,16 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W6">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -3370,7 +3394,7 @@
         <v>97.2</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3394,7 +3418,7 @@
         <v>97.2</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3444,19 +3468,19 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="M8">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P8">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3468,19 +3492,19 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="U8">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="X8">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -3521,19 +3545,19 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3545,19 +3569,19 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W9">
         <v>100</v>
       </c>
       <c r="X9">
-        <v>91.7</v>
+        <v>93.5</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -3598,43 +3622,43 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O10">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="P10">
+        <v>95.7</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>94.40000000000001</v>
       </c>
-      <c r="P10">
-        <v>95.8</v>
-      </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
-        <v>100</v>
-      </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
-        <v>100</v>
-      </c>
       <c r="U10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W10">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X10">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -3678,13 +3702,13 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3702,13 +3726,13 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -3755,16 +3779,16 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="P12">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3779,16 +3803,16 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V12">
         <v>100</v>
       </c>
       <c r="W12">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="X12">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -3829,7 +3853,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -3853,7 +3877,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -3906,7 +3930,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -3915,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3930,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -3939,7 +3963,7 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -3983,16 +4007,16 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>97.2</v>
+        <v>95.8</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N15">
         <v>100</v>
       </c>
       <c r="O15">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4007,16 +4031,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>97.2</v>
+        <v>95.8</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -4060,19 +4084,19 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>91.7</v>
+        <v>90.3</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O16">
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4084,19 +4108,19 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>91.7</v>
+        <v>90.3</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W16">
         <v>100</v>
       </c>
       <c r="X16">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -4137,16 +4161,16 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N17">
         <v>100</v>
       </c>
       <c r="O17">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4161,16 +4185,16 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>94.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X17">
         <v>100</v>
@@ -4214,19 +4238,19 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="M18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O18">
-        <v>72.2</v>
+        <v>81.8</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4238,19 +4262,19 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="U18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W18">
-        <v>72.2</v>
+        <v>81.8</v>
       </c>
       <c r="X18">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -4291,19 +4315,19 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M19">
         <v>90</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O19">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="P19">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4315,19 +4339,19 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U19">
         <v>90</v>
       </c>
       <c r="V19">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W19">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="X19">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -4377,7 +4401,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4401,7 +4425,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -4445,7 +4469,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4454,10 +4478,10 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4469,7 +4493,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>97.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4478,10 +4502,10 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -4522,19 +4546,19 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="M22">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="N22">
         <v>100</v>
       </c>
       <c r="O22">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P22">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4546,19 +4570,19 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="U22">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X22">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -4599,7 +4623,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>88.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4608,23 +4632,23 @@
         <v>100</v>
       </c>
       <c r="O23">
+        <v>97</v>
+      </c>
+      <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>94.40000000000001</v>
       </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
-        <v>100</v>
-      </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
-        <v>88.90000000000001</v>
-      </c>
       <c r="U23">
         <v>100</v>
       </c>
@@ -4632,7 +4656,7 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -4679,16 +4703,16 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P24">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4703,16 +4727,16 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X24">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -4801,7 +4825,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -4810,19 +4834,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="G3" s="2">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4833,7 +4857,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4842,19 +4866,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>85.7</v>
+        <v>95.2</v>
       </c>
       <c r="G4" s="2">
-        <v>14.3</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4865,7 +4889,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -4874,19 +4898,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="G5" s="2">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4897,7 +4921,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -4918,7 +4942,7 @@
         <v>4.8</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4929,7 +4953,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -4938,19 +4962,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4961,7 +4985,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -4970,19 +4994,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>6.3</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4993,7 +5017,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
@@ -5002,19 +5026,19 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5064,7 +5088,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5096,22 +5120,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920215</v>
+        <v>23330051920237</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5119,16 +5143,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920215</v>
+        <v>23330051920237</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5142,19 +5166,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920207</v>
+        <v>23330051920278</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -5165,16 +5189,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920207</v>
+        <v>23330051920278</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5188,39 +5212,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920213</v>
+        <v>23330051920280</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920226</v>
+        <v>23330051920280</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5234,16 +5258,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920216</v>
+        <v>23330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -5257,16 +5281,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920240</v>
+        <v>23330051920226</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -5280,16 +5304,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920244</v>
+        <v>23330051920215</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -5303,16 +5327,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920333</v>
+        <v>23330051920216</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -5326,16 +5350,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920252</v>
+        <v>23330051920240</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -5349,16 +5373,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920239</v>
+        <v>23330051920244</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -5372,16 +5396,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920328</v>
+        <v>23330051920333</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -5395,16 +5419,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920256</v>
+        <v>23330051920252</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -5418,16 +5442,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920257</v>
+        <v>23330051920239</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -5441,16 +5465,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920270</v>
+        <v>23330051920328</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -5464,16 +5488,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920276</v>
+        <v>23330051920256</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -5487,16 +5511,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920277</v>
+        <v>23330051920257</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -5510,16 +5534,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920279</v>
+        <v>23330051920207</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -5528,6 +5552,98 @@
         <v>47</v>
       </c>
       <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920270</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920276</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920277</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920279</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20241.xlsx
+++ b/grupos/3ARHV - Estadisticos 20241.xlsx
@@ -1312,7 +1312,7 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1360,7 +1360,7 @@
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>7</v>
@@ -3471,7 +3471,7 @@
         <v>91.7</v>
       </c>
       <c r="M8">
-        <v>47.5</v>
+        <v>95</v>
       </c>
       <c r="N8">
         <v>90.59999999999999</v>
@@ -3495,7 +3495,7 @@
         <v>91.7</v>
       </c>
       <c r="U8">
-        <v>47.5</v>
+        <v>95</v>
       </c>
       <c r="V8">
         <v>90.59999999999999</v>

--- a/grupos/3ARHV - Estadisticos 20241.xlsx
+++ b/grupos/3ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -164,6 +164,9 @@
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
@@ -173,9 +176,6 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
@@ -197,37 +197,28 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
     <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>VANESA</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
   </si>
   <si>
     <t>ANGEL ABRAHAM</t>
@@ -781,10 +772,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -793,19 +784,19 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>8</v>
@@ -814,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>10</v>
@@ -870,10 +861,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -882,16 +873,16 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -906,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -959,10 +950,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -971,10 +962,10 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -992,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>8</v>
@@ -1048,10 +1039,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1060,10 +1051,10 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1081,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1137,10 +1128,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1149,19 +1140,19 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1226,10 +1217,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1238,10 +1229,10 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1262,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1315,10 +1306,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1327,19 +1318,19 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1348,10 +1339,10 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1404,10 +1395,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1416,16 +1407,16 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1493,10 +1484,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1505,10 +1496,10 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1529,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1582,10 +1573,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1594,16 +1585,16 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1618,7 +1609,7 @@
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1671,10 +1662,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1683,10 +1674,10 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1760,10 +1751,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1772,10 +1763,10 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1849,10 +1840,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1861,10 +1852,10 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1885,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1938,10 +1929,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1950,19 +1941,19 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -1971,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2027,10 +2018,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2039,16 +2030,16 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2060,10 +2051,10 @@
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2116,10 +2107,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2128,19 +2119,19 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2205,10 +2196,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2217,10 +2208,10 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2241,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2294,10 +2285,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2306,10 +2297,10 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2383,10 +2374,10 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2395,19 +2386,19 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2416,10 +2407,10 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2472,10 +2463,10 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2484,10 +2475,10 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2508,7 +2499,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2561,10 +2552,10 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2573,10 +2564,10 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2594,7 +2585,7 @@
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2772,10 +2763,10 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R4">
-        <v>94.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S4">
         <v>97.5</v>
@@ -2784,7 +2775,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -2843,7 +2834,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>91.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S5">
         <v>97.5</v>
@@ -2852,7 +2843,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -2911,7 +2902,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.2</v>
+        <v>98.2</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2920,7 +2911,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U6">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2979,7 +2970,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>97.2</v>
+        <v>98.2</v>
       </c>
       <c r="S7">
         <v>97.5</v>
@@ -3047,7 +3038,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>91.7</v>
+        <v>85.7</v>
       </c>
       <c r="S8">
         <v>95</v>
@@ -3056,10 +3047,10 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U8">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V8">
-        <v>95.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3115,7 +3106,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S9">
         <v>95</v>
@@ -3127,7 +3118,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>93.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3171,7 +3162,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N10">
-        <v>87.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="O10">
         <v>95.7</v>
@@ -3180,10 +3171,10 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R10">
-        <v>94.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S10">
         <v>95</v>
@@ -3192,10 +3183,10 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U10">
-        <v>87.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V10">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3251,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="S11">
         <v>92.5</v>
@@ -3260,7 +3251,7 @@
         <v>100</v>
       </c>
       <c r="U11">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3286,7 +3277,7 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>95.8</v>
@@ -3307,7 +3298,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>95.7</v>
@@ -3316,10 +3307,10 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="S12">
         <v>97.5</v>
@@ -3328,10 +3319,10 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3387,7 +3378,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3452,10 +3443,10 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R14">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3464,7 +3455,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -3523,7 +3514,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>95.8</v>
+        <v>97.3</v>
       </c>
       <c r="S15">
         <v>97.5</v>
@@ -3532,7 +3523,7 @@
         <v>100</v>
       </c>
       <c r="U15">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -3588,10 +3579,10 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R16">
-        <v>90.3</v>
+        <v>90.2</v>
       </c>
       <c r="S16">
         <v>97.5</v>
@@ -3603,7 +3594,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3656,10 +3647,10 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R17">
-        <v>93.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="S17">
         <v>97.5</v>
@@ -3668,7 +3659,7 @@
         <v>100</v>
       </c>
       <c r="U17">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -3694,7 +3685,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -3715,7 +3706,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N18">
-        <v>81.8</v>
+        <v>97</v>
       </c>
       <c r="O18">
         <v>97.8</v>
@@ -3724,10 +3715,10 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R18">
-        <v>97.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S18">
         <v>90</v>
@@ -3736,10 +3727,10 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U18">
-        <v>81.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
-        <v>97.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3762,7 +3753,7 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="H19">
         <v>95.8</v>
@@ -3783,7 +3774,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N19">
-        <v>78.8</v>
+        <v>97</v>
       </c>
       <c r="O19">
         <v>95.7</v>
@@ -3792,10 +3783,10 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R19">
-        <v>94.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S19">
         <v>90</v>
@@ -3804,10 +3795,10 @@
         <v>90.59999999999999</v>
       </c>
       <c r="U19">
-        <v>78.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V19">
-        <v>95.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3872,7 +3863,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -3928,10 +3919,10 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="R21">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3940,10 +3931,10 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V21">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -3996,10 +3987,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>90.3</v>
       </c>
       <c r="R22">
-        <v>91.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="S22">
         <v>87.5</v>
@@ -4008,10 +3999,10 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V22">
-        <v>97.8</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4067,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4076,7 +4067,7 @@
         <v>100</v>
       </c>
       <c r="U23">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4144,10 +4135,10 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V24">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4236,7 +4227,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -4257,7 +4248,7 @@
         <v>4.8</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4268,7 +4259,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4300,7 +4291,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -4321,7 +4312,7 @@
         <v>4.8</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4332,7 +4323,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -4341,19 +4332,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4385,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4487,7 +4478,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4519,22 +4510,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920191</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4542,22 +4533,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920191</v>
+        <v>23330051920278</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4565,22 +4556,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920237</v>
+        <v>23330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4588,22 +4579,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920278</v>
+        <v>23330051920191</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4611,24 +4602,47 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
+        <v>23330051920191</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>23330051920280</v>
       </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20241.xlsx
+++ b/grupos/3ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -161,12 +161,12 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
@@ -203,7 +203,7 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ZACARIAS</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>VALERIO</t>
@@ -212,7 +212,7 @@
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>CANDELARIO</t>
   </si>
   <si>
     <t>OSCAR ALEXANDER</t>
@@ -221,7 +221,7 @@
     <t>DIEGO DE JESUS</t>
   </si>
   <si>
-    <t>ANGEL ABRAHAM</t>
+    <t>DANNA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -778,10 +778,10 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -802,7 +802,7 @@
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -867,10 +867,10 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -956,10 +956,10 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -977,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1045,10 +1045,10 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1069,7 +1069,7 @@
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1223,10 +1223,10 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1312,10 +1312,10 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1401,10 +1401,10 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1490,10 +1490,10 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1511,10 +1511,10 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>5</v>
@@ -1579,10 +1579,10 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1603,7 +1603,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1668,10 +1668,10 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>9</v>
@@ -1757,10 +1757,10 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1778,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1846,10 +1846,10 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1867,10 +1867,10 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -1935,10 +1935,10 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2024,10 +2024,10 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2113,10 +2113,10 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2134,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2202,10 +2202,10 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2291,10 +2291,10 @@
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2380,10 +2380,10 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2469,10 +2469,10 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2490,10 +2490,10 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -2558,10 +2558,10 @@
         <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2579,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>7</v>
@@ -2769,10 +2769,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T4">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U4">
         <v>93.8</v>
@@ -2837,7 +2837,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -2908,7 +2908,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U6">
         <v>93.8</v>
@@ -2973,7 +2973,7 @@
         <v>98.2</v>
       </c>
       <c r="S7">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -3041,10 +3041,10 @@
         <v>85.7</v>
       </c>
       <c r="S8">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T8">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U8">
         <v>97.90000000000001</v>
@@ -3109,10 +3109,10 @@
         <v>99.09999999999999</v>
       </c>
       <c r="S9">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="T9">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3177,10 +3177,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T10">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U10">
         <v>97.90000000000001</v>
@@ -3245,7 +3245,7 @@
         <v>98.2</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -3313,7 +3313,7 @@
         <v>98.2</v>
       </c>
       <c r="S12">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -3517,7 +3517,7 @@
         <v>97.3</v>
       </c>
       <c r="S15">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -3585,10 +3585,10 @@
         <v>90.2</v>
       </c>
       <c r="S16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T16">
-        <v>90.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3653,7 +3653,7 @@
         <v>90.2</v>
       </c>
       <c r="S17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -3721,10 +3721,10 @@
         <v>96.40000000000001</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T18">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U18">
         <v>97.90000000000001</v>
@@ -3789,10 +3789,10 @@
         <v>93.8</v>
       </c>
       <c r="S19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T19">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U19">
         <v>97.90000000000001</v>
@@ -3857,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -3925,7 +3925,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -3993,7 +3993,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="S22">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
@@ -4061,7 +4061,7 @@
         <v>94.59999999999999</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -4129,7 +4129,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
@@ -4204,19 +4204,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="G2" s="2">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -4248,7 +4248,7 @@
         <v>4.8</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>4.8</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4478,7 +4478,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4548,7 +4548,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4571,7 +4571,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4591,10 +4591,10 @@
         <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4602,47 +4602,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920191</v>
+        <v>23330051920256</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920280</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20241.xlsx
+++ b/grupos/3ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="71">
   <si>
     <t>Materia</t>
   </si>
@@ -161,6 +161,9 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -179,9 +182,6 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -200,6 +200,9 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -209,6 +212,9 @@
     <t>VALERIO</t>
   </si>
   <si>
+    <t>FERRER</t>
+  </si>
+  <si>
     <t>VALIENTE</t>
   </si>
   <si>
@@ -216,6 +222,9 @@
   </si>
   <si>
     <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>VANESA</t>
   </si>
   <si>
     <t>DIEGO DE JESUS</t>
@@ -769,7 +778,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -858,7 +867,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -879,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -947,7 +956,7 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -1036,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1125,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1146,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1214,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1303,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1324,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1392,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1481,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>6</v>
@@ -1502,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1570,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1659,7 +1668,7 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1680,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1748,7 +1757,7 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1837,7 +1846,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>6</v>
@@ -1926,7 +1935,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>6</v>
@@ -2015,7 +2024,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>6</v>
@@ -2104,7 +2113,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>6</v>
@@ -2125,7 +2134,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2193,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2282,7 +2291,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2371,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -2392,7 +2401,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2460,7 +2469,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>8</v>
@@ -2549,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>6</v>
@@ -2570,7 +2579,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -3032,7 +3041,7 @@
         <v>95.7</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3984,7 +3993,7 @@
         <v>97.8</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q22">
         <v>90.3</v>
@@ -4195,7 +4204,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
@@ -4204,19 +4213,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>95.2</v>
+        <v>90.5</v>
       </c>
       <c r="G2" s="2">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4227,7 +4236,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -4248,7 +4257,7 @@
         <v>4.8</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4259,7 +4268,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4291,7 +4300,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -4312,7 +4321,7 @@
         <v>4.8</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4323,7 +4332,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -4344,7 +4353,7 @@
         <v>4.8</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4355,7 +4364,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -4364,19 +4373,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4387,7 +4396,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>53</v>
@@ -4408,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4478,7 +4487,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4516,16 +4525,16 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4539,16 +4548,16 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4562,16 +4571,16 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4579,22 +4588,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920191</v>
+        <v>23330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4602,24 +4611,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920256</v>
+        <v>23330051920237</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>50</v>
       </c>
-      <c r="G6">
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920256</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>
